--- a/Stratig_TrvlAT.xlsx
+++ b/Stratig_TrvlAT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\PowerBITables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{734B876A-239F-431C-A4A3-9931A73B1BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B316D4A-8325-44F8-A250-54F900758C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E57AAC1B-91EA-404F-A582-8A9C2308D92D}"/>
   </bookViews>
@@ -85,9 +85,6 @@
     <t>Operational Sector</t>
   </si>
   <si>
-    <t>Primary Station Hub</t>
-  </si>
-  <si>
     <t>Fleet / Systems Class</t>
   </si>
   <si>
@@ -119,6 +116,9 @@
   </si>
   <si>
     <t>Disruption Delay Incidents</t>
+  </si>
+  <si>
+    <t>Region</t>
   </si>
 </sst>
 </file>
@@ -775,18 +775,6 @@
   </cellStyles>
   <dxfs count="11">
     <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="6" formatCode="#,##0_);[Red]\(#,##0\)"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -920,6 +908,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -927,18 +924,21 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -955,16 +955,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A11A64C0-8491-40C9-BB03-ED88387276EF}" name="Table1" displayName="Table1" ref="A1:G10" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A11A64C0-8491-40C9-BB03-ED88387276EF}" name="Table1" displayName="Table1" ref="A1:G10" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="A1:G10" xr:uid="{A11A64C0-8491-40C9-BB03-ED88387276EF}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{86708DFD-C916-4FC4-AEAA-51B750A94603}" name="Carrier/Agency Code Travel Transit Entity" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{48A0AF2E-FD53-40CC-BD06-8AF90D4AB873}" name="Operational Sector" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{30496B13-A5F6-4A80-9011-BB73054F8E39}" name="Primary Station Hub" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{5B08AEAA-46B2-4C02-A9DE-6C254C4B0852}" name="Fleet / Systems Class" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{DC33EED5-2416-4A4D-9719-F64ED9B0207D}" name="Daily Dispatched Legs Allocated" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{19B11AA3-1EB3-4B79-A5A6-ABDA85BAAD1C}" name="Capital Expenditure (CapEx)" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{C1EC1865-87E1-46FB-9698-A1CCEA564365}" name="Disruption Delay Incidents" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{86708DFD-C916-4FC4-AEAA-51B750A94603}" name="Carrier/Agency Code Travel Transit Entity" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{48A0AF2E-FD53-40CC-BD06-8AF90D4AB873}" name="Operational Sector" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{30496B13-A5F6-4A80-9011-BB73054F8E39}" name="Region" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{5B08AEAA-46B2-4C02-A9DE-6C254C4B0852}" name="Fleet / Systems Class" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{DC33EED5-2416-4A4D-9719-F64ED9B0207D}" name="Daily Dispatched Legs Allocated" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{19B11AA3-1EB3-4B79-A5A6-ABDA85BAAD1C}" name="Capital Expenditure (CapEx)" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{C1EC1865-87E1-46FB-9698-A1CCEA564365}" name="Disruption Delay Incidents" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1307,19 +1307,19 @@
         <v>20</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>22</v>
-      </c>
       <c r="E1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>31</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -1333,7 +1333,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E2" s="2">
         <v>18500</v>
@@ -1356,7 +1356,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3" s="2">
         <v>45000</v>
@@ -1379,7 +1379,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2">
         <v>32000</v>
@@ -1402,7 +1402,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5" s="2">
         <v>850</v>
@@ -1425,7 +1425,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6" s="2">
         <v>1200</v>
@@ -1448,7 +1448,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E7" s="2">
         <v>450</v>
@@ -1471,7 +1471,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E8" s="2">
         <v>4200</v>
@@ -1494,7 +1494,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E9" s="2">
         <v>3900</v>
@@ -1517,7 +1517,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E10" s="11">
         <v>4400</v>

--- a/Stratig_TrvlAT.xlsx
+++ b/Stratig_TrvlAT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\PowerBITables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B316D4A-8325-44F8-A250-54F900758C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E8366F-5CA6-4381-966E-4E1D900DA765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E57AAC1B-91EA-404F-A582-8A9C2308D92D}"/>
   </bookViews>
@@ -52,9 +52,6 @@
     <t>CHICAGO-ORD</t>
   </si>
   <si>
-    <t>Carrier/Agency Code Travel Transit Entity</t>
-  </si>
-  <si>
     <t>AAA-DOM-01 American Automobile Association (AAA)</t>
   </si>
   <si>
@@ -119,6 +116,9 @@
   </si>
   <si>
     <t>Region</t>
+  </si>
+  <si>
+    <t>Commend Tier</t>
   </si>
 </sst>
 </file>
@@ -958,7 +958,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A11A64C0-8491-40C9-BB03-ED88387276EF}" name="Table1" displayName="Table1" ref="A1:G10" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="A1:G10" xr:uid="{A11A64C0-8491-40C9-BB03-ED88387276EF}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{86708DFD-C916-4FC4-AEAA-51B750A94603}" name="Carrier/Agency Code Travel Transit Entity" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{86708DFD-C916-4FC4-AEAA-51B750A94603}" name="Commend Tier" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{48A0AF2E-FD53-40CC-BD06-8AF90D4AB873}" name="Operational Sector" dataDxfId="5"/>
     <tableColumn id="3" xr3:uid="{30496B13-A5F6-4A80-9011-BB73054F8E39}" name="Region" dataDxfId="4"/>
     <tableColumn id="4" xr3:uid="{5B08AEAA-46B2-4C02-A9DE-6C254C4B0852}" name="Fleet / Systems Class" dataDxfId="3"/>
@@ -1301,30 +1301,30 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>21</v>
-      </c>
       <c r="E1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -1333,7 +1333,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2" s="2">
         <v>18500</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" s="2">
         <v>45000</v>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>0</v>
@@ -1379,7 +1379,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4" s="2">
         <v>32000</v>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>4</v>
@@ -1402,7 +1402,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2">
         <v>850</v>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
@@ -1425,7 +1425,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2">
         <v>1200</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>4</v>
@@ -1448,7 +1448,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E7" s="2">
         <v>450</v>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
@@ -1471,7 +1471,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8" s="2">
         <v>4200</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
@@ -1494,7 +1494,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E9" s="2">
         <v>3900</v>
@@ -1508,7 +1508,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>7</v>
@@ -1517,7 +1517,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E10" s="11">
         <v>4400</v>
